--- a/musique.xlsx
+++ b/musique.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jm/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90FC7E71-2A1B-AC48-8FA0-CED940FCA92C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B74BCA0-F40D-794D-8AA7-B4960000EEB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2516,7 +2516,7 @@
     </row>
     <row r="2" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
-        <v>46266</v>
+        <v>45901</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>11</v>
@@ -2551,7 +2551,7 @@
     </row>
     <row r="3" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
-        <v>46268</v>
+        <v>45903</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>20</v>
@@ -2586,7 +2586,7 @@
     </row>
     <row r="4" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
-        <v>46269</v>
+        <v>45904</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>27</v>
@@ -2621,7 +2621,7 @@
     </row>
     <row r="5" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
-        <v>46272</v>
+        <v>45907</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>35</v>
@@ -2656,7 +2656,7 @@
     </row>
     <row r="6" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
-        <v>46273</v>
+        <v>45908</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>43</v>
@@ -2691,7 +2691,7 @@
     </row>
     <row r="7" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
-        <v>46275</v>
+        <v>45910</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>35</v>
@@ -2724,7 +2724,7 @@
     </row>
     <row r="8" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
-        <v>46276</v>
+        <v>45911</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>35</v>
@@ -2759,7 +2759,7 @@
     </row>
     <row r="9" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
-        <v>46279</v>
+        <v>45914</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>43</v>
@@ -2794,7 +2794,7 @@
     </row>
     <row r="10" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
-        <v>46280</v>
+        <v>45915</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>27</v>
@@ -2829,7 +2829,7 @@
     </row>
     <row r="11" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
-        <v>46282</v>
+        <v>45917</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>20</v>
@@ -2862,7 +2862,7 @@
     </row>
     <row r="12" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
-        <v>46283</v>
+        <v>45918</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>20</v>
@@ -2895,7 +2895,7 @@
     </row>
     <row r="13" spans="1:11" ht="48" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
-        <v>46286</v>
+        <v>45921</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>20</v>
@@ -2930,7 +2930,7 @@
     </row>
     <row r="14" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
-        <v>46287</v>
+        <v>45922</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>35</v>
@@ -2965,7 +2965,7 @@
     </row>
     <row r="15" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
-        <v>46289</v>
+        <v>45924</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>20</v>
@@ -3000,7 +3000,7 @@
     </row>
     <row r="16" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
-        <v>46290</v>
+        <v>45925</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>96</v>
@@ -3035,7 +3035,7 @@
     </row>
     <row r="17" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
-        <v>46293</v>
+        <v>45928</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>20</v>
@@ -3070,7 +3070,7 @@
     </row>
     <row r="18" spans="1:11" ht="48" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
-        <v>46294</v>
+        <v>45929</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>109</v>
@@ -3105,7 +3105,7 @@
     </row>
     <row r="19" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
-        <v>46296</v>
+        <v>45931</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>20</v>
@@ -3140,7 +3140,7 @@
     </row>
     <row r="20" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
-        <v>46297</v>
+        <v>45932</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>109</v>
@@ -3175,7 +3175,7 @@
     </row>
     <row r="21" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
-        <v>46300</v>
+        <v>45935</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>20</v>
@@ -3210,7 +3210,7 @@
     </row>
     <row r="22" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
-        <v>46301</v>
+        <v>45936</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>131</v>
@@ -3245,7 +3245,7 @@
     </row>
     <row r="23" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
-        <v>46303</v>
+        <v>45938</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>20</v>
@@ -3280,7 +3280,7 @@
     </row>
     <row r="24" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
-        <v>46304</v>
+        <v>45939</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>43</v>
@@ -3315,7 +3315,7 @@
     </row>
     <row r="25" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
-        <v>46307</v>
+        <v>45942</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>20</v>
@@ -3350,7 +3350,7 @@
     </row>
     <row r="26" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
-        <v>46308</v>
+        <v>45943</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>155</v>
@@ -3385,7 +3385,7 @@
     </row>
     <row r="27" spans="1:11" ht="48" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
-        <v>46310</v>
+        <v>45945</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>20</v>
@@ -3420,7 +3420,7 @@
     </row>
     <row r="28" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
-        <v>46311</v>
+        <v>45946</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>165</v>
@@ -3455,7 +3455,7 @@
     </row>
     <row r="29" spans="1:11" ht="48" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
-        <v>46328</v>
+        <v>45963</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>20</v>
@@ -3490,7 +3490,7 @@
     </row>
     <row r="30" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
-        <v>46329</v>
+        <v>45964</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>27</v>
@@ -3525,7 +3525,7 @@
     </row>
     <row r="31" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
-        <v>46331</v>
+        <v>45966</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>20</v>
@@ -3560,7 +3560,7 @@
     </row>
     <row r="32" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
-        <v>46332</v>
+        <v>45967</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>11</v>
@@ -3595,7 +3595,7 @@
     </row>
     <row r="33" spans="1:11" ht="48" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
-        <v>46335</v>
+        <v>45970</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>20</v>
@@ -3630,7 +3630,7 @@
     </row>
     <row r="34" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
-        <v>46336</v>
+        <v>45971</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>11</v>
@@ -3665,7 +3665,7 @@
     </row>
     <row r="35" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
-        <v>46338</v>
+        <v>45973</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>20</v>
@@ -3700,7 +3700,7 @@
     </row>
     <row r="36" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
-        <v>46339</v>
+        <v>45974</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>20</v>
@@ -3735,7 +3735,7 @@
     </row>
     <row r="37" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
-        <v>46342</v>
+        <v>45977</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>20</v>
@@ -3770,7 +3770,7 @@
     </row>
     <row r="38" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
-        <v>46343</v>
+        <v>45978</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>35</v>
@@ -3805,7 +3805,7 @@
     </row>
     <row r="39" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
-        <v>46345</v>
+        <v>45980</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>20</v>
@@ -3840,7 +3840,7 @@
     </row>
     <row r="40" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
-        <v>46346</v>
+        <v>45981</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>35</v>
@@ -3875,7 +3875,7 @@
     </row>
     <row r="41" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
-        <v>46349</v>
+        <v>45984</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>20</v>
@@ -3910,7 +3910,7 @@
     </row>
     <row r="42" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
-        <v>46350</v>
+        <v>45985</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>20</v>
@@ -3945,7 +3945,7 @@
     </row>
     <row r="43" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
-        <v>46352</v>
+        <v>45987</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>20</v>
@@ -3978,7 +3978,7 @@
     </row>
     <row r="44" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
-        <v>46353</v>
+        <v>45988</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>43</v>
@@ -4011,7 +4011,7 @@
     </row>
     <row r="45" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
-        <v>46356</v>
+        <v>45991</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>20</v>
@@ -4046,7 +4046,7 @@
     </row>
     <row r="46" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
-        <v>46357</v>
+        <v>45992</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>43</v>
@@ -4081,7 +4081,7 @@
     </row>
     <row r="47" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
-        <v>46359</v>
+        <v>45994</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>20</v>
@@ -4116,7 +4116,7 @@
     </row>
     <row r="48" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
-        <v>46360</v>
+        <v>45995</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>27</v>
@@ -4151,7 +4151,7 @@
     </row>
     <row r="49" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
-        <v>46363</v>
+        <v>45998</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>20</v>
@@ -4186,7 +4186,7 @@
     </row>
     <row r="50" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
-        <v>46364</v>
+        <v>45999</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>109</v>
@@ -4221,7 +4221,7 @@
     </row>
     <row r="51" spans="1:11" ht="48" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
-        <v>46366</v>
+        <v>46001</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>20</v>
@@ -4256,7 +4256,7 @@
     </row>
     <row r="52" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
-        <v>46367</v>
+        <v>46002</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>109</v>
@@ -4291,7 +4291,7 @@
     </row>
     <row r="53" spans="1:11" ht="48" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
-        <v>46370</v>
+        <v>46005</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>20</v>
@@ -4326,7 +4326,7 @@
     </row>
     <row r="54" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
-        <v>46371</v>
+        <v>46006</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>11</v>
@@ -4361,7 +4361,7 @@
     </row>
     <row r="55" spans="1:11" ht="48" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
-        <v>46373</v>
+        <v>46008</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>20</v>
@@ -4396,7 +4396,7 @@
     </row>
     <row r="56" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
-        <v>46374</v>
+        <v>46009</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>20</v>
